--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:41</t>
+    <t xml:space="preserve">2026-09-09 22:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:27</t>
+    <t xml:space="preserve">2026-09-12 19:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:44</t>
+    <t xml:space="preserve">2026-09-24 00:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:22</t>
+    <t xml:space="preserve">2026-09-27 22:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:10</t>
+    <t xml:space="preserve">2026-10-01 20:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:51</t>
+    <t xml:space="preserve">2026-10-02 13:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_biobio.xlsx
@@ -39,7 +39,7 @@
     <t xml:space="preserve">San Pedro de la Paz</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Concepción</t>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Florida</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Hualqui</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:18</t>
+    <t xml:space="preserve">2026-10-04 08:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2020_biobio.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:03</t>
+    <t xml:space="preserve">2026-10-05 07:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
